--- a/example1-metabolomics/results-A/pca/pca_norm_HFDDam_over_RDDam.xlsx
+++ b/example1-metabolomics/results-A/pca/pca_norm_HFDDam_over_RDDam.xlsx
@@ -500,43 +500,43 @@
         <v>14</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.343762329808779</v>
+        <v>-0.341325005102185</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0986100693216116</v>
+        <v>0.122926049810455</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.371233707057463</v>
+        <v>-0.357724816204532</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0135051091212122</v>
+        <v>0.0730991260002351</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0119422718964912</v>
+        <v>-0.0292418302031727</v>
       </c>
       <c r="G2" t="n">
-        <v>0.171203775275009</v>
+        <v>-0.175403153690304</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0594570524140505</v>
+        <v>-0.0758200581770775</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0595734037741135</v>
+        <v>-0.0630144669574993</v>
       </c>
       <c r="J2" t="n">
-        <v>0.239365113189818</v>
+        <v>-0.214753640840804</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.0778254580460773</v>
+        <v>-0.114581607393886</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.135602278659875</v>
+        <v>0.163381774955547</v>
       </c>
       <c r="M2" t="n">
-        <v>0.143912015524814</v>
+        <v>0.129265866064944</v>
       </c>
       <c r="N2" t="n">
-        <v>0.203266382328395</v>
+        <v>-0.0510572814459203</v>
       </c>
     </row>
     <row r="3">
@@ -544,43 +544,43 @@
         <v>15</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.2926320487071</v>
+        <v>-0.2935696388923</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0344068270691034</v>
+        <v>0.0340356838221516</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0079095779459935</v>
+        <v>0.000735513600306041</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0983831769334793</v>
+        <v>-0.086222534869299</v>
       </c>
       <c r="F3" t="n">
-        <v>0.17946704870487</v>
+        <v>0.17489988858802</v>
       </c>
       <c r="G3" t="n">
-        <v>0.315036723624609</v>
+        <v>-0.298135031723501</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0883709094300751</v>
+        <v>-0.100313759692264</v>
       </c>
       <c r="I3" t="n">
-        <v>0.33088179388516</v>
+        <v>0.255067568588276</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0610973672819378</v>
+        <v>0.176445190961636</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0363606161038744</v>
+        <v>0.00498574923148647</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.237061707533775</v>
+        <v>0.300952586601284</v>
       </c>
       <c r="M3" t="n">
-        <v>0.460535005459971</v>
+        <v>0.485030658201268</v>
       </c>
       <c r="N3" t="n">
-        <v>0.067172750960407</v>
+        <v>-0.118207111427031</v>
       </c>
     </row>
     <row r="4">
@@ -588,43 +588,43 @@
         <v>16</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.315210823587803</v>
+        <v>-0.314195116120091</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.168792214815857</v>
+        <v>-0.149116176443882</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.139807048414833</v>
+        <v>-0.191572019369334</v>
       </c>
       <c r="E4" t="n">
-        <v>0.122606526639582</v>
+        <v>-0.115634989642473</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0839304456773706</v>
+        <v>0.0534149031467433</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.48572381684172</v>
+        <v>0.479497757086815</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0906839469599148</v>
+        <v>0.112185076975599</v>
       </c>
       <c r="I4" t="n">
-        <v>0.127582487211677</v>
+        <v>0.14945511618782</v>
       </c>
       <c r="J4" t="n">
-        <v>0.232939336842226</v>
+        <v>-0.218198132432436</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.106241325211265</v>
+        <v>-0.0547021811892088</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.391683071987984</v>
+        <v>0.380929252585151</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.328327136319216</v>
+        <v>-0.310853145888275</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0391278000601862</v>
+        <v>-0.230833637890366</v>
       </c>
     </row>
     <row r="5">
@@ -632,43 +632,43 @@
         <v>17</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.0986341160014969</v>
+        <v>-0.0981124521365183</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.146496207722672</v>
+        <v>-0.144671072125914</v>
       </c>
       <c r="D5" t="n">
-        <v>0.356744388719784</v>
+        <v>0.240644884617619</v>
       </c>
       <c r="E5" t="n">
-        <v>0.271839921860969</v>
+        <v>-0.384504507946027</v>
       </c>
       <c r="F5" t="n">
-        <v>0.138445548996641</v>
+        <v>0.130661010979162</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.247279626798843</v>
+        <v>0.219275356573241</v>
       </c>
       <c r="H5" t="n">
-        <v>0.228944156477498</v>
+        <v>0.221278191384719</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.128529061441437</v>
+        <v>-0.0831273442281893</v>
       </c>
       <c r="J5" t="n">
-        <v>0.225365053040782</v>
+        <v>-0.233419640127976</v>
       </c>
       <c r="K5" t="n">
-        <v>0.199573953805415</v>
+        <v>0.186693161740988</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.017624224760559</v>
+        <v>0.0438553818098962</v>
       </c>
       <c r="M5" t="n">
-        <v>0.320606390901053</v>
+        <v>0.30127982093173</v>
       </c>
       <c r="N5" t="n">
-        <v>0.142857961438555</v>
+        <v>-0.11074062180347</v>
       </c>
     </row>
     <row r="6">
@@ -676,43 +676,43 @@
         <v>18</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.131616183340772</v>
+        <v>-0.134135179913868</v>
       </c>
       <c r="C6" t="n">
-        <v>0.293211336827466</v>
+        <v>0.253764819872472</v>
       </c>
       <c r="D6" t="n">
-        <v>0.571408774479551</v>
+        <v>0.595198431846159</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0230033471267286</v>
+        <v>-0.0747272982635787</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.27222216766957</v>
+        <v>-0.226819283474357</v>
       </c>
       <c r="G6" t="n">
-        <v>0.21210854041025</v>
+        <v>-0.220896637779975</v>
       </c>
       <c r="H6" t="n">
-        <v>0.137319411249062</v>
+        <v>0.132026371999838</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0158478463498608</v>
+        <v>0.0393524816313255</v>
       </c>
       <c r="J6" t="n">
-        <v>0.276253556509383</v>
+        <v>-0.299660255047315</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.286564463918715</v>
+        <v>-0.275119327506177</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.235246093574274</v>
+        <v>0.234435336717616</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0139004894370496</v>
+        <v>-0.0685424472603004</v>
       </c>
       <c r="N6" t="n">
-        <v>0.045151045272261</v>
+        <v>-0.0460391962407812</v>
       </c>
     </row>
     <row r="7">
@@ -720,43 +720,43 @@
         <v>19</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.263346151207989</v>
+        <v>-0.26277789862536</v>
       </c>
       <c r="C7" t="n">
-        <v>0.183496472816238</v>
+        <v>0.188961218633566</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0513285649912785</v>
+        <v>-0.0606303310737802</v>
       </c>
       <c r="E7" t="n">
-        <v>0.155780482823994</v>
+        <v>-0.126977363285289</v>
       </c>
       <c r="F7" t="n">
-        <v>0.087414969454965</v>
+        <v>0.062383679135515</v>
       </c>
       <c r="G7" t="n">
-        <v>0.113082072091659</v>
+        <v>-0.108131876815506</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.021657359334501</v>
+        <v>-0.0197216128635797</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0518370047626385</v>
+        <v>-0.110563830003702</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3995882374571</v>
+        <v>0.411944657902317</v>
       </c>
       <c r="K7" t="n">
-        <v>0.169055433217029</v>
+        <v>0.153766635720098</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.104834676231133</v>
+        <v>0.0867515393355344</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0265474965719557</v>
+        <v>-0.00394615732615274</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0937546983392073</v>
+        <v>-0.376952769012247</v>
       </c>
     </row>
     <row r="8">
@@ -764,43 +764,43 @@
         <v>20</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.308727015681656</v>
+        <v>-0.308029719497433</v>
       </c>
       <c r="C8" t="n">
-        <v>0.409652760950693</v>
+        <v>0.399821136362444</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.020105685811908</v>
+        <v>0.047067792147127</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0609565790400482</v>
+        <v>0.102112873884449</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.525246730386987</v>
+        <v>-0.531843407535661</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.351955367499283</v>
+        <v>0.338917868820482</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.214730779839522</v>
+        <v>-0.207783274375294</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0172015334310489</v>
+        <v>0.0283427551223191</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.159987436136602</v>
+        <v>0.140054970193057</v>
       </c>
       <c r="K8" t="n">
-        <v>0.187577209842082</v>
+        <v>0.186039369831445</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0938065049066815</v>
+        <v>-0.11223777526582</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.021003177063093</v>
+        <v>-0.0350566569036055</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0463945117553207</v>
+        <v>0.051410462556896</v>
       </c>
     </row>
     <row r="9">
@@ -808,43 +808,43 @@
         <v>21</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0804279137554507</v>
+        <v>-0.0802912110101257</v>
       </c>
       <c r="C9" t="n">
-        <v>0.08656181294695</v>
+        <v>0.080798152135686</v>
       </c>
       <c r="D9" t="n">
-        <v>0.294753260812201</v>
+        <v>0.245639863652393</v>
       </c>
       <c r="E9" t="n">
-        <v>0.103757350479614</v>
+        <v>-0.186853955032688</v>
       </c>
       <c r="F9" t="n">
-        <v>0.135025491227102</v>
+        <v>0.144400275600278</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.027099699237461</v>
+        <v>0.0231284958831248</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0694216775230586</v>
+        <v>-0.0873023799543858</v>
       </c>
       <c r="I9" t="n">
-        <v>0.154551902427774</v>
+        <v>0.162420918023909</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0237537912338815</v>
+        <v>-0.0129129916398492</v>
       </c>
       <c r="K9" t="n">
-        <v>0.436633776156256</v>
+        <v>0.476744293405672</v>
       </c>
       <c r="L9" t="n">
-        <v>0.180857470678847</v>
+        <v>-0.195169162527219</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.325179302519887</v>
+        <v>-0.21171543799529</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0778410078361965</v>
+        <v>-0.201203311146448</v>
       </c>
     </row>
     <row r="10">
@@ -852,43 +852,43 @@
         <v>22</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.0794420916002899</v>
+        <v>-0.0818445559926349</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0679457781697611</v>
+        <v>0.0503222183557729</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0663656966090359</v>
+        <v>0.117664474171727</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0964548510626586</v>
+        <v>0.105750415913977</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0212839813599693</v>
+        <v>0.0235866351328175</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0375302427054941</v>
+        <v>0.0737191833545497</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.204592699502272</v>
+        <v>-0.16830819009601</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0785003434875736</v>
+        <v>-0.111731717982225</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.237064865741725</v>
+        <v>0.213216896064677</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.344617980446527</v>
+        <v>-0.340754581691118</v>
       </c>
       <c r="L10" t="n">
-        <v>0.252371312446741</v>
+        <v>-0.261777319121736</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0000458180513076066</v>
+        <v>-0.00752807532145893</v>
       </c>
       <c r="N10" t="n">
-        <v>0.264583511269943</v>
+        <v>-0.247579520396501</v>
       </c>
     </row>
     <row r="11">
@@ -896,43 +896,43 @@
         <v>23</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0140493657616486</v>
+        <v>0.017571050284738</v>
       </c>
       <c r="C11" t="n">
-        <v>0.328493910005128</v>
+        <v>0.322419150631297</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0992244822253108</v>
+        <v>0.0342071321806397</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.75601432805402</v>
+        <v>0.713800667859504</v>
       </c>
       <c r="F11" t="n">
-        <v>0.356987516720203</v>
+        <v>0.419689047133034</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.106532091048562</v>
+        <v>0.122756841516461</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0579557724401577</v>
+        <v>0.0560025489606719</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0086209241980651</v>
+        <v>0.0389543705249528</v>
       </c>
       <c r="J11" t="n">
-        <v>0.185129454069655</v>
+        <v>-0.196302704645837</v>
       </c>
       <c r="K11" t="n">
-        <v>0.200836152841071</v>
+        <v>0.223401534583087</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.139824288502219</v>
+        <v>0.143912821851577</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0573289188657879</v>
+        <v>0.050782680892736</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0631764403023959</v>
+        <v>-0.067058038220771</v>
       </c>
     </row>
     <row r="12">
@@ -940,43 +940,43 @@
         <v>24</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.334191166268709</v>
+        <v>-0.329683007427666</v>
       </c>
       <c r="C12" t="n">
-        <v>0.291515650616443</v>
+        <v>0.313050416244355</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.103849079384875</v>
+        <v>-0.135376310028462</v>
       </c>
       <c r="E12" t="n">
-        <v>0.107275482817835</v>
+        <v>-0.10043705798242</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0343880714296839</v>
+        <v>0.0206189742037619</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0347357570465405</v>
+        <v>-0.0765714883171143</v>
       </c>
       <c r="H12" t="n">
-        <v>0.484393305475232</v>
+        <v>0.45906404461613</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0572410634724876</v>
+        <v>0.0886851991985724</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0227571097746944</v>
+        <v>-0.0407898367677616</v>
       </c>
       <c r="K12" t="n">
-        <v>0.069061079441588</v>
+        <v>0.0601662552781978</v>
       </c>
       <c r="L12" t="n">
-        <v>0.376563921171761</v>
+        <v>-0.375785481449725</v>
       </c>
       <c r="M12" t="n">
-        <v>0.00977271509051653</v>
+        <v>0.0408456580152992</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.318002401062713</v>
+        <v>0.310300423422734</v>
       </c>
     </row>
     <row r="13">
@@ -984,43 +984,43 @@
         <v>25</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.143883526132449</v>
+        <v>-0.146305323445761</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.117735887511917</v>
+        <v>-0.131233946532251</v>
       </c>
       <c r="D13" t="n">
-        <v>0.11959863820721</v>
+        <v>0.138359150317171</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0868011972756349</v>
+        <v>0.0694481456711261</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.12836083515563</v>
+        <v>-0.10353554003071</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0586162795087736</v>
+        <v>-0.0409139901283562</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.3702836813896</v>
+        <v>-0.378032787253083</v>
       </c>
       <c r="I13" t="n">
-        <v>0.169522128552378</v>
+        <v>0.178535123030395</v>
       </c>
       <c r="J13" t="n">
-        <v>0.326982155580036</v>
+        <v>-0.288136023999771</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0239653140257045</v>
+        <v>0.0285909411425134</v>
       </c>
       <c r="L13" t="n">
-        <v>0.224526440717394</v>
+        <v>-0.180378269824398</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0867843808921163</v>
+        <v>0.186941724106672</v>
       </c>
       <c r="N13" t="n">
-        <v>0.282717090355603</v>
+        <v>0.17800541681854</v>
       </c>
     </row>
     <row r="14">
@@ -1028,43 +1028,43 @@
         <v>26</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.128021535822988</v>
+        <v>-0.128764949646425</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.29352768708898</v>
+        <v>-0.29278796604152</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0479639064449883</v>
+        <v>-0.0438578072756478</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.129984365077349</v>
+        <v>0.127834055407106</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.068097473682616</v>
+        <v>-0.0513714434936803</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0386174705756177</v>
+        <v>0.0380681416845793</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0968227292937804</v>
+        <v>-0.102460355187852</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.00904730518743449</v>
+        <v>0.00382651350024088</v>
       </c>
       <c r="J14" t="n">
-        <v>0.046900176805251</v>
+        <v>-0.0476296276257865</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0751904568715078</v>
+        <v>0.0448738438959347</v>
       </c>
       <c r="L14" t="n">
-        <v>0.373665216095327</v>
+        <v>-0.339834359820276</v>
       </c>
       <c r="M14" t="n">
-        <v>0.37304582655284</v>
+        <v>0.389963603380719</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.135161045369715</v>
+        <v>-0.289923146851095</v>
       </c>
     </row>
     <row r="15">
@@ -1072,43 +1072,43 @@
         <v>27</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.0947180231831861</v>
+        <v>-0.099081418736995</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0708032216864972</v>
+        <v>-0.0991898408951684</v>
       </c>
       <c r="D15" t="n">
-        <v>0.11892663807087</v>
+        <v>0.186783045545053</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.139219119439654</v>
+        <v>0.148617486432542</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.116089714846904</v>
+        <v>-0.109429716524997</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0169531804744382</v>
+        <v>0.0350452708433644</v>
       </c>
       <c r="H15" t="n">
-        <v>0.144585207154355</v>
+        <v>0.183795901718779</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.256353672920867</v>
+        <v>-0.270724655135699</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0626774846345421</v>
+        <v>0.0624376962795492</v>
       </c>
       <c r="K15" t="n">
-        <v>0.150912975009607</v>
+        <v>0.220134075374559</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.093949788879204</v>
+        <v>0.113099710228828</v>
       </c>
       <c r="M15" t="n">
-        <v>0.172041253993958</v>
+        <v>0.227549323051985</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0988950347461518</v>
+        <v>0.243493215078396</v>
       </c>
     </row>
     <row r="16">
@@ -1116,43 +1116,43 @@
         <v>28</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.107693329286499</v>
+        <v>-0.11060861846534</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0594638450609533</v>
+        <v>0.0421572897574965</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0568403042523863</v>
+        <v>0.104166388577192</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0552031152914557</v>
+        <v>0.0702076398496366</v>
       </c>
       <c r="F16" t="n">
-        <v>0.044745366918577</v>
+        <v>0.0381203382426184</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0930102373622334</v>
+        <v>0.131450418575004</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.136425360030751</v>
+        <v>-0.0896604642649186</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.166708252360997</v>
+        <v>-0.183234531761615</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0226194340035493</v>
+        <v>-0.0445336815078873</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.378796625246301</v>
+        <v>-0.336136074057488</v>
       </c>
       <c r="L16" t="n">
-        <v>0.161622161078275</v>
+        <v>-0.160457688753136</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.122173549336408</v>
+        <v>-0.0770200618825927</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0235316931047014</v>
+        <v>-0.302990267415099</v>
       </c>
     </row>
     <row r="17">
@@ -1160,43 +1160,43 @@
         <v>29</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.3585190595238</v>
+        <v>-0.357925102618434</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.202115478728584</v>
+        <v>-0.184596092419159</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.193603166037885</v>
+        <v>-0.211524130509067</v>
       </c>
       <c r="E17" t="n">
-        <v>0.00541024257338564</v>
+        <v>0.0318089006079156</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0278168158416819</v>
+        <v>0.0385858811946244</v>
       </c>
       <c r="G17" t="n">
-        <v>0.426694265423357</v>
+        <v>-0.432364379626306</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0221579586084218</v>
+        <v>-0.00616791675064045</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0520103048659927</v>
+        <v>-0.0398282187399763</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0724152499074127</v>
+        <v>-0.0995255266769654</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0142154796506989</v>
+        <v>-0.01429959114454</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0649427080296494</v>
+        <v>-0.0978184214620366</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.405006917271843</v>
+        <v>-0.388585831155426</v>
       </c>
       <c r="N17" t="n">
-        <v>0.117949743439867</v>
+        <v>0.0982453434913038</v>
       </c>
     </row>
     <row r="18">
@@ -1204,43 +1204,43 @@
         <v>30</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.213581130822128</v>
+        <v>-0.213600376139754</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0119075173272939</v>
+        <v>0.00322952133741954</v>
       </c>
       <c r="D18" t="n">
-        <v>0.358338991949722</v>
+        <v>0.315287687415475</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0477110974678959</v>
+        <v>-0.0753205421244765</v>
       </c>
       <c r="F18" t="n">
-        <v>0.526836159877679</v>
+        <v>0.550543166179125</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0310945999312811</v>
+        <v>-0.00325172456288867</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.124632033118497</v>
+        <v>-0.117255203449669</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.139953589653327</v>
+        <v>-0.140559930689742</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.155028427068827</v>
+        <v>0.107802925091552</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0406463099203403</v>
+        <v>-0.0458314013122731</v>
       </c>
       <c r="L18" t="n">
-        <v>0.168537337196839</v>
+        <v>-0.203350968780775</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.16458780163955</v>
+        <v>-0.193429648364306</v>
       </c>
       <c r="N18" t="n">
-        <v>0.044660604148116</v>
+        <v>0.16192526339946</v>
       </c>
     </row>
     <row r="19">
@@ -1248,43 +1248,43 @@
         <v>31</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.102723703864649</v>
+        <v>-0.106027390528793</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0143585981791727</v>
+        <v>-0.00871196526719079</v>
       </c>
       <c r="D19" t="n">
-        <v>0.124365088572017</v>
+        <v>0.180206485323949</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.119272213949196</v>
+        <v>0.11955699612582</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0171569714544019</v>
+        <v>-0.00472439968232843</v>
       </c>
       <c r="G19" t="n">
-        <v>0.099755493421863</v>
+        <v>-0.0698884200892153</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0803922655207234</v>
+        <v>-0.0491139224333347</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.231562345897178</v>
+        <v>-0.242674700000422</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0138068112212484</v>
+        <v>-0.0298650138661252</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.246100701133369</v>
+        <v>-0.225073835575246</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.154232693763489</v>
+        <v>0.158225956661645</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0655030057248378</v>
+        <v>0.0409782752928409</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.556790565422243</v>
+        <v>0.0760486657855698</v>
       </c>
     </row>
     <row r="20">
@@ -1292,43 +1292,43 @@
         <v>32</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.274762588959624</v>
+        <v>-0.2761796976249</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.282719982730821</v>
+        <v>-0.28588348106914</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0808204813209172</v>
+        <v>0.0639061390626557</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0621355508766516</v>
+        <v>0.0281336632254136</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0177058189602209</v>
+        <v>0.0280699964756922</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.17910298895526</v>
+        <v>0.19447560363322</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.355477638899776</v>
+        <v>-0.345423081227539</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.206019264428424</v>
+        <v>-0.209188786771909</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.185468148893745</v>
+        <v>0.153491984902703</v>
       </c>
       <c r="K20" t="n">
-        <v>0.148393790289735</v>
+        <v>0.121101194571692</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.25878454327958</v>
+        <v>0.228981294506044</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0487655974380632</v>
+        <v>-0.0571905022854461</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.241931001578069</v>
+        <v>0.395191484774173</v>
       </c>
     </row>
     <row r="21">
@@ -1336,43 +1336,43 @@
         <v>33</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.177170037353961</v>
+        <v>-0.177036550817538</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0749972363649823</v>
+        <v>-0.0684605916910812</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.109311162395427</v>
+        <v>-0.112485638161087</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0000766976793892689</v>
+        <v>0.0153992817438249</v>
       </c>
       <c r="F21" t="n">
-        <v>0.144649270741513</v>
+        <v>0.121581664983188</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.321286176309436</v>
+        <v>0.328046483179562</v>
       </c>
       <c r="H21" t="n">
-        <v>0.220224816298073</v>
+        <v>0.257714078658743</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.087536450150031</v>
+        <v>-0.0822096105181624</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0591343186922797</v>
+        <v>-0.0721241700834549</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.318411632959939</v>
+        <v>-0.298398089949749</v>
       </c>
       <c r="L21" t="n">
-        <v>0.241617986190168</v>
+        <v>-0.217681286415033</v>
       </c>
       <c r="M21" t="n">
-        <v>0.178380186282156</v>
+        <v>0.20184608555043</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0782303125398145</v>
+        <v>0.113727750401345</v>
       </c>
     </row>
     <row r="22">
@@ -1380,43 +1380,43 @@
         <v>34</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.0514524315991843</v>
+        <v>-0.0547456175211342</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.12076716914444</v>
+        <v>-0.142644415890415</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0575781641503984</v>
+        <v>0.116896583011186</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.145092088624032</v>
+        <v>0.159710238822744</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.095492211484655</v>
+        <v>-0.0879730835719521</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0058606841087842</v>
+        <v>0.014206500161669</v>
       </c>
       <c r="H22" t="n">
-        <v>0.345695454068849</v>
+        <v>0.384505983602394</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0379428664922794</v>
+        <v>-0.0736772685638062</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.515970891730356</v>
+        <v>0.499232196169245</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.103526614207482</v>
+        <v>-0.0583630462704928</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.158902099453923</v>
+        <v>0.130778693700907</v>
       </c>
       <c r="M22" t="n">
-        <v>0.039168073387703</v>
+        <v>-0.0105717221570452</v>
       </c>
       <c r="N22" t="n">
-        <v>0.439750590337945</v>
+        <v>0.0142473500968716</v>
       </c>
     </row>
     <row r="23">
@@ -1424,43 +1424,43 @@
         <v>35</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.120021662260408</v>
+        <v>-0.120573680533256</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.274881428350772</v>
+        <v>-0.286595443759943</v>
       </c>
       <c r="D23" t="n">
-        <v>0.182406694631528</v>
+        <v>0.19712476440187</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.308839954276913</v>
+        <v>0.232998134497928</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0959802941651631</v>
+        <v>-0.0346059723512065</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0599330671487433</v>
+        <v>0.0468959782381594</v>
       </c>
       <c r="H23" t="n">
-        <v>0.130050842098976</v>
+        <v>0.110140393093048</v>
       </c>
       <c r="I23" t="n">
-        <v>0.689222744028168</v>
+        <v>0.712831140124543</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.154117326209422</v>
+        <v>0.184474647567085</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.138947383136704</v>
+        <v>-0.140065842101687</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0304430308638727</v>
+        <v>-0.0425649523434405</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0603592743101519</v>
+        <v>-0.0866647251675774</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.213374101295979</v>
+        <v>0.0546852414670035</v>
       </c>
     </row>
     <row r="24">
@@ -1468,43 +1468,43 @@
         <v>36</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.118985808104749</v>
+        <v>-0.121372344545775</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.348158370108656</v>
+        <v>-0.363269260214781</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0587092695170075</v>
+        <v>0.104406999404298</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.293045981626842</v>
+        <v>0.279628612164892</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.28585737190357</v>
+        <v>-0.237821524246243</v>
       </c>
       <c r="G24" t="n">
-        <v>0.179546709289091</v>
+        <v>-0.196961086967791</v>
       </c>
       <c r="H24" t="n">
-        <v>0.241117910692208</v>
+        <v>0.233847071106933</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.304502528399953</v>
+        <v>-0.236291974931302</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0994226653645928</v>
+        <v>-0.173491344508352</v>
       </c>
       <c r="K24" t="n">
-        <v>0.229705577659534</v>
+        <v>0.272313468886498</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0767029875161379</v>
+        <v>-0.104051037943129</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.141923301528644</v>
+        <v>-0.138233497611096</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.00749696630803428</v>
+        <v>-0.296078540738599</v>
       </c>
     </row>
   </sheetData>

--- a/example1-metabolomics/results-A/pca/pca_norm_HFDDam_over_RDDam.xlsx
+++ b/example1-metabolomics/results-A/pca/pca_norm_HFDDam_over_RDDam.xlsx
@@ -500,43 +500,43 @@
         <v>14</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.341325005102185</v>
+        <v>-0.343762329808779</v>
       </c>
       <c r="C2" t="n">
-        <v>0.122926049810455</v>
+        <v>0.0986100693216116</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.357724816204532</v>
+        <v>-0.371233707057463</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0730991260002351</v>
+        <v>0.0135051091212122</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0292418302031727</v>
+        <v>-0.0119422718964912</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.175403153690304</v>
+        <v>0.171203775275009</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0758200581770775</v>
+        <v>-0.0594570524140505</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0630144669574993</v>
+        <v>-0.0595734037741135</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.214753640840804</v>
+        <v>0.239365113189818</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.114581607393886</v>
+        <v>-0.0778254580460773</v>
       </c>
       <c r="L2" t="n">
-        <v>0.163381774955547</v>
+        <v>-0.135602278659875</v>
       </c>
       <c r="M2" t="n">
-        <v>0.129265866064944</v>
+        <v>0.143912015524814</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0510572814459203</v>
+        <v>0.203266382328395</v>
       </c>
     </row>
     <row r="3">
@@ -544,43 +544,43 @@
         <v>15</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.2935696388923</v>
+        <v>-0.2926320487071</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0340356838221516</v>
+        <v>0.0344068270691034</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000735513600306041</v>
+        <v>0.0079095779459935</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.086222534869299</v>
+        <v>0.0983831769334793</v>
       </c>
       <c r="F3" t="n">
-        <v>0.17489988858802</v>
+        <v>0.17946704870487</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.298135031723501</v>
+        <v>0.315036723624609</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.100313759692264</v>
+        <v>-0.0883709094300751</v>
       </c>
       <c r="I3" t="n">
-        <v>0.255067568588276</v>
+        <v>0.33088179388516</v>
       </c>
       <c r="J3" t="n">
-        <v>0.176445190961636</v>
+        <v>-0.0610973672819378</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00498574923148647</v>
+        <v>0.0363606161038744</v>
       </c>
       <c r="L3" t="n">
-        <v>0.300952586601284</v>
+        <v>-0.237061707533775</v>
       </c>
       <c r="M3" t="n">
-        <v>0.485030658201268</v>
+        <v>0.460535005459971</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.118207111427031</v>
+        <v>0.067172750960407</v>
       </c>
     </row>
     <row r="4">
@@ -588,43 +588,43 @@
         <v>16</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.314195116120091</v>
+        <v>-0.315210823587803</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.149116176443882</v>
+        <v>-0.168792214815857</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.191572019369334</v>
+        <v>-0.139807048414833</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.115634989642473</v>
+        <v>0.122606526639582</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0534149031467433</v>
+        <v>0.0839304456773706</v>
       </c>
       <c r="G4" t="n">
-        <v>0.479497757086815</v>
+        <v>-0.48572381684172</v>
       </c>
       <c r="H4" t="n">
-        <v>0.112185076975599</v>
+        <v>0.0906839469599148</v>
       </c>
       <c r="I4" t="n">
-        <v>0.14945511618782</v>
+        <v>0.127582487211677</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.218198132432436</v>
+        <v>0.232939336842226</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0547021811892088</v>
+        <v>-0.106241325211265</v>
       </c>
       <c r="L4" t="n">
-        <v>0.380929252585151</v>
+        <v>-0.391683071987984</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.310853145888275</v>
+        <v>-0.328327136319216</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.230833637890366</v>
+        <v>0.0391278000601862</v>
       </c>
     </row>
     <row r="5">
@@ -632,43 +632,43 @@
         <v>17</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.0981124521365183</v>
+        <v>-0.0986341160014969</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.144671072125914</v>
+        <v>-0.146496207722672</v>
       </c>
       <c r="D5" t="n">
-        <v>0.240644884617619</v>
+        <v>0.356744388719784</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.384504507946027</v>
+        <v>0.271839921860969</v>
       </c>
       <c r="F5" t="n">
-        <v>0.130661010979162</v>
+        <v>0.138445548996641</v>
       </c>
       <c r="G5" t="n">
-        <v>0.219275356573241</v>
+        <v>-0.247279626798843</v>
       </c>
       <c r="H5" t="n">
-        <v>0.221278191384719</v>
+        <v>0.228944156477498</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0831273442281893</v>
+        <v>-0.128529061441437</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.233419640127976</v>
+        <v>0.225365053040782</v>
       </c>
       <c r="K5" t="n">
-        <v>0.186693161740988</v>
+        <v>0.199573953805415</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0438553818098962</v>
+        <v>-0.017624224760559</v>
       </c>
       <c r="M5" t="n">
-        <v>0.30127982093173</v>
+        <v>0.320606390901053</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.11074062180347</v>
+        <v>0.142857961438555</v>
       </c>
     </row>
     <row r="6">
@@ -676,43 +676,43 @@
         <v>18</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.134135179913868</v>
+        <v>-0.131616183340772</v>
       </c>
       <c r="C6" t="n">
-        <v>0.253764819872472</v>
+        <v>0.293211336827466</v>
       </c>
       <c r="D6" t="n">
-        <v>0.595198431846159</v>
+        <v>0.571408774479551</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0747272982635787</v>
+        <v>-0.0230033471267286</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.226819283474357</v>
+        <v>-0.27222216766957</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.220896637779975</v>
+        <v>0.21210854041025</v>
       </c>
       <c r="H6" t="n">
-        <v>0.132026371999838</v>
+        <v>0.137319411249062</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0393524816313255</v>
+        <v>-0.0158478463498608</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.299660255047315</v>
+        <v>0.276253556509383</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.275119327506177</v>
+        <v>-0.286564463918715</v>
       </c>
       <c r="L6" t="n">
-        <v>0.234435336717616</v>
+        <v>-0.235246093574274</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0685424472603004</v>
+        <v>-0.0139004894370496</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0460391962407812</v>
+        <v>0.045151045272261</v>
       </c>
     </row>
     <row r="7">
@@ -720,43 +720,43 @@
         <v>19</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.26277789862536</v>
+        <v>-0.263346151207989</v>
       </c>
       <c r="C7" t="n">
-        <v>0.188961218633566</v>
+        <v>0.183496472816238</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0606303310737802</v>
+        <v>-0.0513285649912785</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.126977363285289</v>
+        <v>0.155780482823994</v>
       </c>
       <c r="F7" t="n">
-        <v>0.062383679135515</v>
+        <v>0.087414969454965</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.108131876815506</v>
+        <v>0.113082072091659</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0197216128635797</v>
+        <v>-0.021657359334501</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.110563830003702</v>
+        <v>-0.0518370047626385</v>
       </c>
       <c r="J7" t="n">
-        <v>0.411944657902317</v>
+        <v>-0.3995882374571</v>
       </c>
       <c r="K7" t="n">
-        <v>0.153766635720098</v>
+        <v>0.169055433217029</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0867515393355344</v>
+        <v>-0.104834676231133</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.00394615732615274</v>
+        <v>0.0265474965719557</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.376952769012247</v>
+        <v>-0.0937546983392073</v>
       </c>
     </row>
     <row r="8">
@@ -764,43 +764,43 @@
         <v>20</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.308029719497433</v>
+        <v>-0.308727015681656</v>
       </c>
       <c r="C8" t="n">
-        <v>0.399821136362444</v>
+        <v>0.409652760950693</v>
       </c>
       <c r="D8" t="n">
-        <v>0.047067792147127</v>
+        <v>-0.020105685811908</v>
       </c>
       <c r="E8" t="n">
-        <v>0.102112873884449</v>
+        <v>-0.0609565790400482</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.531843407535661</v>
+        <v>-0.525246730386987</v>
       </c>
       <c r="G8" t="n">
-        <v>0.338917868820482</v>
+        <v>-0.351955367499283</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.207783274375294</v>
+        <v>-0.214730779839522</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0283427551223191</v>
+        <v>0.0172015334310489</v>
       </c>
       <c r="J8" t="n">
-        <v>0.140054970193057</v>
+        <v>-0.159987436136602</v>
       </c>
       <c r="K8" t="n">
-        <v>0.186039369831445</v>
+        <v>0.187577209842082</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.11223777526582</v>
+        <v>0.0938065049066815</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0350566569036055</v>
+        <v>-0.021003177063093</v>
       </c>
       <c r="N8" t="n">
-        <v>0.051410462556896</v>
+        <v>0.0463945117553207</v>
       </c>
     </row>
     <row r="9">
@@ -808,43 +808,43 @@
         <v>21</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0802912110101257</v>
+        <v>-0.0804279137554507</v>
       </c>
       <c r="C9" t="n">
-        <v>0.080798152135686</v>
+        <v>0.08656181294695</v>
       </c>
       <c r="D9" t="n">
-        <v>0.245639863652393</v>
+        <v>0.294753260812201</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.186853955032688</v>
+        <v>0.103757350479614</v>
       </c>
       <c r="F9" t="n">
-        <v>0.144400275600278</v>
+        <v>0.135025491227102</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0231284958831248</v>
+        <v>-0.027099699237461</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0873023799543858</v>
+        <v>-0.0694216775230586</v>
       </c>
       <c r="I9" t="n">
-        <v>0.162420918023909</v>
+        <v>0.154551902427774</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0129129916398492</v>
+        <v>0.0237537912338815</v>
       </c>
       <c r="K9" t="n">
-        <v>0.476744293405672</v>
+        <v>0.436633776156256</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.195169162527219</v>
+        <v>0.180857470678847</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.21171543799529</v>
+        <v>-0.325179302519887</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.201203311146448</v>
+        <v>0.0778410078361965</v>
       </c>
     </row>
     <row r="10">
@@ -852,43 +852,43 @@
         <v>22</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.0818445559926349</v>
+        <v>-0.0794420916002899</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0503222183557729</v>
+        <v>0.0679457781697611</v>
       </c>
       <c r="D10" t="n">
-        <v>0.117664474171727</v>
+        <v>0.0663656966090359</v>
       </c>
       <c r="E10" t="n">
-        <v>0.105750415913977</v>
+        <v>-0.0964548510626586</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0235866351328175</v>
+        <v>0.0212839813599693</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0737191833545497</v>
+        <v>-0.0375302427054941</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.16830819009601</v>
+        <v>-0.204592699502272</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.111731717982225</v>
+        <v>-0.0785003434875736</v>
       </c>
       <c r="J10" t="n">
-        <v>0.213216896064677</v>
+        <v>-0.237064865741725</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.340754581691118</v>
+        <v>-0.344617980446527</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.261777319121736</v>
+        <v>0.252371312446741</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.00752807532145893</v>
+        <v>0.0000458180513076066</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.247579520396501</v>
+        <v>0.264583511269943</v>
       </c>
     </row>
     <row r="11">
@@ -896,43 +896,43 @@
         <v>23</v>
       </c>
       <c r="B11" t="n">
-        <v>0.017571050284738</v>
+        <v>0.0140493657616486</v>
       </c>
       <c r="C11" t="n">
-        <v>0.322419150631297</v>
+        <v>0.328493910005128</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0342071321806397</v>
+        <v>-0.0992244822253108</v>
       </c>
       <c r="E11" t="n">
-        <v>0.713800667859504</v>
+        <v>-0.75601432805402</v>
       </c>
       <c r="F11" t="n">
-        <v>0.419689047133034</v>
+        <v>0.356987516720203</v>
       </c>
       <c r="G11" t="n">
-        <v>0.122756841516461</v>
+        <v>-0.106532091048562</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0560025489606719</v>
+        <v>0.0579557724401577</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0389543705249528</v>
+        <v>-0.0086209241980651</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.196302704645837</v>
+        <v>0.185129454069655</v>
       </c>
       <c r="K11" t="n">
-        <v>0.223401534583087</v>
+        <v>0.200836152841071</v>
       </c>
       <c r="L11" t="n">
-        <v>0.143912821851577</v>
+        <v>-0.139824288502219</v>
       </c>
       <c r="M11" t="n">
-        <v>0.050782680892736</v>
+        <v>0.0573289188657879</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.067058038220771</v>
+        <v>0.0631764403023959</v>
       </c>
     </row>
     <row r="12">
@@ -940,43 +940,43 @@
         <v>24</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.329683007427666</v>
+        <v>-0.334191166268709</v>
       </c>
       <c r="C12" t="n">
-        <v>0.313050416244355</v>
+        <v>0.291515650616443</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.135376310028462</v>
+        <v>-0.103849079384875</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.10043705798242</v>
+        <v>0.107275482817835</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0206189742037619</v>
+        <v>0.0343880714296839</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0765714883171143</v>
+        <v>0.0347357570465405</v>
       </c>
       <c r="H12" t="n">
-        <v>0.45906404461613</v>
+        <v>0.484393305475232</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0886851991985724</v>
+        <v>0.0572410634724876</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.0407898367677616</v>
+        <v>0.0227571097746944</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0601662552781978</v>
+        <v>0.069061079441588</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.375785481449725</v>
+        <v>0.376563921171761</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0408456580152992</v>
+        <v>0.00977271509051653</v>
       </c>
       <c r="N12" t="n">
-        <v>0.310300423422734</v>
+        <v>-0.318002401062713</v>
       </c>
     </row>
     <row r="13">
@@ -984,43 +984,43 @@
         <v>25</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.146305323445761</v>
+        <v>-0.143883526132449</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.131233946532251</v>
+        <v>-0.117735887511917</v>
       </c>
       <c r="D13" t="n">
-        <v>0.138359150317171</v>
+        <v>0.11959863820721</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0694481456711261</v>
+        <v>-0.0868011972756349</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.10353554003071</v>
+        <v>-0.12836083515563</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0409139901283562</v>
+        <v>0.0586162795087736</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.378032787253083</v>
+        <v>-0.3702836813896</v>
       </c>
       <c r="I13" t="n">
-        <v>0.178535123030395</v>
+        <v>0.169522128552378</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.288136023999771</v>
+        <v>0.326982155580036</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0285909411425134</v>
+        <v>0.0239653140257045</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.180378269824398</v>
+        <v>0.224526440717394</v>
       </c>
       <c r="M13" t="n">
-        <v>0.186941724106672</v>
+        <v>0.0867843808921163</v>
       </c>
       <c r="N13" t="n">
-        <v>0.17800541681854</v>
+        <v>0.282717090355603</v>
       </c>
     </row>
     <row r="14">
@@ -1028,43 +1028,43 @@
         <v>26</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.128764949646425</v>
+        <v>-0.128021535822988</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.29278796604152</v>
+        <v>-0.29352768708898</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0438578072756478</v>
+        <v>-0.0479639064449883</v>
       </c>
       <c r="E14" t="n">
-        <v>0.127834055407106</v>
+        <v>-0.129984365077349</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0513714434936803</v>
+        <v>-0.068097473682616</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0380681416845793</v>
+        <v>-0.0386174705756177</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.102460355187852</v>
+        <v>-0.0968227292937804</v>
       </c>
       <c r="I14" t="n">
-        <v>0.00382651350024088</v>
+        <v>-0.00904730518743449</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0476296276257865</v>
+        <v>0.046900176805251</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0448738438959347</v>
+        <v>0.0751904568715078</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.339834359820276</v>
+        <v>0.373665216095327</v>
       </c>
       <c r="M14" t="n">
-        <v>0.389963603380719</v>
+        <v>0.37304582655284</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.289923146851095</v>
+        <v>-0.135161045369715</v>
       </c>
     </row>
     <row r="15">
@@ -1072,43 +1072,43 @@
         <v>27</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.099081418736995</v>
+        <v>-0.0947180231831861</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0991898408951684</v>
+        <v>-0.0708032216864972</v>
       </c>
       <c r="D15" t="n">
-        <v>0.186783045545053</v>
+        <v>0.11892663807087</v>
       </c>
       <c r="E15" t="n">
-        <v>0.148617486432542</v>
+        <v>-0.139219119439654</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.109429716524997</v>
+        <v>-0.116089714846904</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0350452708433644</v>
+        <v>-0.0169531804744382</v>
       </c>
       <c r="H15" t="n">
-        <v>0.183795901718779</v>
+        <v>0.144585207154355</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.270724655135699</v>
+        <v>-0.256353672920867</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0624376962795492</v>
+        <v>-0.0626774846345421</v>
       </c>
       <c r="K15" t="n">
-        <v>0.220134075374559</v>
+        <v>0.150912975009607</v>
       </c>
       <c r="L15" t="n">
-        <v>0.113099710228828</v>
+        <v>-0.093949788879204</v>
       </c>
       <c r="M15" t="n">
-        <v>0.227549323051985</v>
+        <v>0.172041253993958</v>
       </c>
       <c r="N15" t="n">
-        <v>0.243493215078396</v>
+        <v>0.0988950347461518</v>
       </c>
     </row>
     <row r="16">
@@ -1116,43 +1116,43 @@
         <v>28</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.11060861846534</v>
+        <v>-0.107693329286499</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0421572897574965</v>
+        <v>0.0594638450609533</v>
       </c>
       <c r="D16" t="n">
-        <v>0.104166388577192</v>
+        <v>0.0568403042523863</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0702076398496366</v>
+        <v>-0.0552031152914557</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0381203382426184</v>
+        <v>0.044745366918577</v>
       </c>
       <c r="G16" t="n">
-        <v>0.131450418575004</v>
+        <v>-0.0930102373622334</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0896604642649186</v>
+        <v>-0.136425360030751</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.183234531761615</v>
+        <v>-0.166708252360997</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.0445336815078873</v>
+        <v>0.0226194340035493</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.336136074057488</v>
+        <v>-0.378796625246301</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.160457688753136</v>
+        <v>0.161622161078275</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0770200618825927</v>
+        <v>-0.122173549336408</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.302990267415099</v>
+        <v>-0.0235316931047014</v>
       </c>
     </row>
     <row r="17">
@@ -1160,43 +1160,43 @@
         <v>29</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.357925102618434</v>
+        <v>-0.3585190595238</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.184596092419159</v>
+        <v>-0.202115478728584</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.211524130509067</v>
+        <v>-0.193603166037885</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0318089006079156</v>
+        <v>0.00541024257338564</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0385858811946244</v>
+        <v>0.0278168158416819</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.432364379626306</v>
+        <v>0.426694265423357</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.00616791675064045</v>
+        <v>0.0221579586084218</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0398282187399763</v>
+        <v>-0.0520103048659927</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0995255266769654</v>
+        <v>0.0724152499074127</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.01429959114454</v>
+        <v>-0.0142154796506989</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0978184214620366</v>
+        <v>0.0649427080296494</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.388585831155426</v>
+        <v>-0.405006917271843</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0982453434913038</v>
+        <v>0.117949743439867</v>
       </c>
     </row>
     <row r="18">
@@ -1204,43 +1204,43 @@
         <v>30</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.213600376139754</v>
+        <v>-0.213581130822128</v>
       </c>
       <c r="C18" t="n">
-        <v>0.00322952133741954</v>
+        <v>0.0119075173272939</v>
       </c>
       <c r="D18" t="n">
-        <v>0.315287687415475</v>
+        <v>0.358338991949722</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0753205421244765</v>
+        <v>-0.0477110974678959</v>
       </c>
       <c r="F18" t="n">
-        <v>0.550543166179125</v>
+        <v>0.526836159877679</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.00325172456288867</v>
+        <v>0.0310945999312811</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.117255203449669</v>
+        <v>-0.124632033118497</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.140559930689742</v>
+        <v>-0.139953589653327</v>
       </c>
       <c r="J18" t="n">
-        <v>0.107802925091552</v>
+        <v>-0.155028427068827</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0458314013122731</v>
+        <v>-0.0406463099203403</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.203350968780775</v>
+        <v>0.168537337196839</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.193429648364306</v>
+        <v>-0.16458780163955</v>
       </c>
       <c r="N18" t="n">
-        <v>0.16192526339946</v>
+        <v>0.044660604148116</v>
       </c>
     </row>
     <row r="19">
@@ -1248,43 +1248,43 @@
         <v>31</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.106027390528793</v>
+        <v>-0.102723703864649</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.00871196526719079</v>
+        <v>0.0143585981791727</v>
       </c>
       <c r="D19" t="n">
-        <v>0.180206485323949</v>
+        <v>0.124365088572017</v>
       </c>
       <c r="E19" t="n">
-        <v>0.11955699612582</v>
+        <v>-0.119272213949196</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.00472439968232843</v>
+        <v>-0.0171569714544019</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0698884200892153</v>
+        <v>0.099755493421863</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0491139224333347</v>
+        <v>-0.0803922655207234</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.242674700000422</v>
+        <v>-0.231562345897178</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0298650138661252</v>
+        <v>0.0138068112212484</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.225073835575246</v>
+        <v>-0.246100701133369</v>
       </c>
       <c r="L19" t="n">
-        <v>0.158225956661645</v>
+        <v>-0.154232693763489</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0409782752928409</v>
+        <v>0.0655030057248378</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0760486657855698</v>
+        <v>-0.556790565422243</v>
       </c>
     </row>
     <row r="20">
@@ -1292,43 +1292,43 @@
         <v>32</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.2761796976249</v>
+        <v>-0.274762588959624</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.28588348106914</v>
+        <v>-0.282719982730821</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0639061390626557</v>
+        <v>0.0808204813209172</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0281336632254136</v>
+        <v>-0.0621355508766516</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0280699964756922</v>
+        <v>0.0177058189602209</v>
       </c>
       <c r="G20" t="n">
-        <v>0.19447560363322</v>
+        <v>-0.17910298895526</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.345423081227539</v>
+        <v>-0.355477638899776</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.209188786771909</v>
+        <v>-0.206019264428424</v>
       </c>
       <c r="J20" t="n">
-        <v>0.153491984902703</v>
+        <v>-0.185468148893745</v>
       </c>
       <c r="K20" t="n">
-        <v>0.121101194571692</v>
+        <v>0.148393790289735</v>
       </c>
       <c r="L20" t="n">
-        <v>0.228981294506044</v>
+        <v>-0.25878454327958</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0571905022854461</v>
+        <v>0.0487655974380632</v>
       </c>
       <c r="N20" t="n">
-        <v>0.395191484774173</v>
+        <v>-0.241931001578069</v>
       </c>
     </row>
     <row r="21">
@@ -1336,43 +1336,43 @@
         <v>33</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.177036550817538</v>
+        <v>-0.177170037353961</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0684605916910812</v>
+        <v>-0.0749972363649823</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.112485638161087</v>
+        <v>-0.109311162395427</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0153992817438249</v>
+        <v>0.0000766976793892689</v>
       </c>
       <c r="F21" t="n">
-        <v>0.121581664983188</v>
+        <v>0.144649270741513</v>
       </c>
       <c r="G21" t="n">
-        <v>0.328046483179562</v>
+        <v>-0.321286176309436</v>
       </c>
       <c r="H21" t="n">
-        <v>0.257714078658743</v>
+        <v>0.220224816298073</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0822096105181624</v>
+        <v>-0.087536450150031</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0721241700834549</v>
+        <v>0.0591343186922797</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.298398089949749</v>
+        <v>-0.318411632959939</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.217681286415033</v>
+        <v>0.241617986190168</v>
       </c>
       <c r="M21" t="n">
-        <v>0.20184608555043</v>
+        <v>0.178380186282156</v>
       </c>
       <c r="N21" t="n">
-        <v>0.113727750401345</v>
+        <v>0.0782303125398145</v>
       </c>
     </row>
     <row r="22">
@@ -1380,43 +1380,43 @@
         <v>34</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.0547456175211342</v>
+        <v>-0.0514524315991843</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.142644415890415</v>
+        <v>-0.12076716914444</v>
       </c>
       <c r="D22" t="n">
-        <v>0.116896583011186</v>
+        <v>0.0575781641503984</v>
       </c>
       <c r="E22" t="n">
-        <v>0.159710238822744</v>
+        <v>-0.145092088624032</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0879730835719521</v>
+        <v>-0.095492211484655</v>
       </c>
       <c r="G22" t="n">
-        <v>0.014206500161669</v>
+        <v>-0.0058606841087842</v>
       </c>
       <c r="H22" t="n">
-        <v>0.384505983602394</v>
+        <v>0.345695454068849</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0736772685638062</v>
+        <v>-0.0379428664922794</v>
       </c>
       <c r="J22" t="n">
-        <v>0.499232196169245</v>
+        <v>-0.515970891730356</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.0583630462704928</v>
+        <v>-0.103526614207482</v>
       </c>
       <c r="L22" t="n">
-        <v>0.130778693700907</v>
+        <v>-0.158902099453923</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0105717221570452</v>
+        <v>0.039168073387703</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0142473500968716</v>
+        <v>0.439750590337945</v>
       </c>
     </row>
     <row r="23">
@@ -1424,43 +1424,43 @@
         <v>35</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.120573680533256</v>
+        <v>-0.120021662260408</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.286595443759943</v>
+        <v>-0.274881428350772</v>
       </c>
       <c r="D23" t="n">
-        <v>0.19712476440187</v>
+        <v>0.182406694631528</v>
       </c>
       <c r="E23" t="n">
-        <v>0.232998134497928</v>
+        <v>-0.308839954276913</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0346059723512065</v>
+        <v>-0.0959802941651631</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0468959782381594</v>
+        <v>-0.0599330671487433</v>
       </c>
       <c r="H23" t="n">
-        <v>0.110140393093048</v>
+        <v>0.130050842098976</v>
       </c>
       <c r="I23" t="n">
-        <v>0.712831140124543</v>
+        <v>0.689222744028168</v>
       </c>
       <c r="J23" t="n">
-        <v>0.184474647567085</v>
+        <v>-0.154117326209422</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.140065842101687</v>
+        <v>-0.138947383136704</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.0425649523434405</v>
+        <v>0.0304430308638727</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0866647251675774</v>
+        <v>-0.0603592743101519</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0546852414670035</v>
+        <v>-0.213374101295979</v>
       </c>
     </row>
     <row r="24">
@@ -1468,43 +1468,43 @@
         <v>36</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.121372344545775</v>
+        <v>-0.118985808104749</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.363269260214781</v>
+        <v>-0.348158370108656</v>
       </c>
       <c r="D24" t="n">
-        <v>0.104406999404298</v>
+        <v>0.0587092695170075</v>
       </c>
       <c r="E24" t="n">
-        <v>0.279628612164892</v>
+        <v>-0.293045981626842</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.237821524246243</v>
+        <v>-0.28585737190357</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.196961086967791</v>
+        <v>0.179546709289091</v>
       </c>
       <c r="H24" t="n">
-        <v>0.233847071106933</v>
+        <v>0.241117910692208</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.236291974931302</v>
+        <v>-0.304502528399953</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.173491344508352</v>
+        <v>0.0994226653645928</v>
       </c>
       <c r="K24" t="n">
-        <v>0.272313468886498</v>
+        <v>0.229705577659534</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.104051037943129</v>
+        <v>0.0767029875161379</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.138233497611096</v>
+        <v>-0.141923301528644</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.296078540738599</v>
+        <v>-0.00749696630803428</v>
       </c>
     </row>
   </sheetData>
